--- a/artfynd/A 19427-2025 artfynd.xlsx
+++ b/artfynd/A 19427-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>113679388</v>
       </c>
       <c r="B2" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79310</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,12 +770,12 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -789,12 +784,7 @@
         <v>113679389</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79310</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,12 +876,12 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>

--- a/artfynd/A 19427-2025 artfynd.xlsx
+++ b/artfynd/A 19427-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679388</v>
       </c>
       <c r="B2" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113679389</v>
       </c>
       <c r="B3" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19427-2025 artfynd.xlsx
+++ b/artfynd/A 19427-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679388</v>
       </c>
       <c r="B2" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113679389</v>
       </c>
       <c r="B3" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19427-2025 artfynd.xlsx
+++ b/artfynd/A 19427-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679388</v>
       </c>
       <c r="B2" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113679389</v>
       </c>
       <c r="B3" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19427-2025 artfynd.xlsx
+++ b/artfynd/A 19427-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679388</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113679389</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19427-2025 artfynd.xlsx
+++ b/artfynd/A 19427-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679388</v>
       </c>
       <c r="B2" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113679389</v>
       </c>
       <c r="B3" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19427-2025 artfynd.xlsx
+++ b/artfynd/A 19427-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679388</v>
       </c>
       <c r="B2" t="n">
-        <v>79329</v>
+        <v>79332</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113679389</v>
       </c>
       <c r="B3" t="n">
-        <v>79329</v>
+        <v>79332</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19427-2025 artfynd.xlsx
+++ b/artfynd/A 19427-2025 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>113679388</v>
       </c>
       <c r="B2" t="n">
-        <v>79332</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -784,11 +784,11 @@
         <v>113679389</v>
       </c>
       <c r="B3" t="n">
-        <v>79332</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
